--- a/Planificacion_Anagra_Final_MCP_SDD.xlsx
+++ b/Planificacion_Anagra_Final_MCP_SDD.xlsx
@@ -1,28 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andres/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\desafIA\Presentaciones\Presentacion_Anagra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B29B97D-08B9-A148-87CF-717B0649925D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F39B8D8-8524-4148-8D5F-C2F891F363AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planificación" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
     <sheet name="Referencias" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="202">
   <si>
     <t>Clase</t>
   </si>
@@ -673,25 +686,25 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -925,19 +938,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="46.5" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="120.83203125" customWidth="1"/>
+    <col min="4" max="4" width="120.796875" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="44.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:9" ht="27.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,7 +979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15">
+    <row r="2" spans="1:9">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -991,7 +1004,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="15">
+    <row r="3" spans="1:9">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1016,7 +1029,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:9" ht="15">
+    <row r="4" spans="1:9">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1043,7 +1056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15">
+    <row r="5" spans="1:9">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1070,7 +1083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15">
+    <row r="6" spans="1:9">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -1097,7 +1110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15">
+    <row r="7" spans="1:9">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -1124,7 +1137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15">
+    <row r="8" spans="1:9">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -1151,7 +1164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15">
+    <row r="9" spans="1:9">
       <c r="A9" s="4">
         <v>1</v>
       </c>
@@ -1176,7 +1189,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" ht="15">
+    <row r="10" spans="1:9">
       <c r="A10" s="4">
         <v>2</v>
       </c>
@@ -1203,7 +1216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15">
+    <row r="11" spans="1:9">
       <c r="A11" s="4">
         <v>2</v>
       </c>
@@ -1214,25 +1227,17 @@
         <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="5">
-        <v>5</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -1243,25 +1248,17 @@
         <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="5">
-        <v>10</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15">
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="4">
         <v>2</v>
       </c>
@@ -1272,25 +1269,17 @@
         <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="5">
-        <v>10</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15">
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -1301,25 +1290,25 @@
         <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="H14" s="5">
         <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="4">
         <v>2</v>
       </c>
@@ -1330,25 +1319,25 @@
         <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H15" s="5">
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="4">
         <v>2</v>
       </c>
@@ -1359,25 +1348,25 @@
         <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5">
         <v>10</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="4">
         <v>2</v>
       </c>
@@ -1388,25 +1377,25 @@
         <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H17" s="5">
         <v>5</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="4">
         <v>2</v>
       </c>
@@ -1417,25 +1406,25 @@
         <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H18" s="5">
         <v>10</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="4">
         <v>2</v>
       </c>
@@ -1446,50 +1435,48 @@
         <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5">
         <v>10</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="4">
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H20" s="5">
-        <v>10</v>
-      </c>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" ht="15">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1516,7 +1503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15">
+    <row r="22" spans="1:9">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1543,7 +1530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15">
+    <row r="23" spans="1:9">
       <c r="A23" s="4">
         <v>3</v>
       </c>
@@ -1572,7 +1559,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15">
+    <row r="24" spans="1:9">
       <c r="A24" s="4">
         <v>3</v>
       </c>
@@ -1601,7 +1588,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15">
+    <row r="25" spans="1:9">
       <c r="A25" s="4">
         <v>3</v>
       </c>
@@ -1630,7 +1617,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15">
+    <row r="26" spans="1:9">
       <c r="A26" s="4">
         <v>3</v>
       </c>
@@ -1659,7 +1646,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15">
+    <row r="27" spans="1:9">
       <c r="A27" s="4">
         <v>3</v>
       </c>
@@ -1688,7 +1675,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15">
+    <row r="28" spans="1:9">
       <c r="A28" s="4">
         <v>3</v>
       </c>
@@ -1717,7 +1704,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15">
+    <row r="29" spans="1:9">
       <c r="A29" s="4">
         <v>3</v>
       </c>
@@ -1746,7 +1733,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15">
+    <row r="30" spans="1:9">
       <c r="A30" s="4">
         <v>3</v>
       </c>
@@ -1775,7 +1762,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15">
+    <row r="31" spans="1:9">
       <c r="A31" s="4">
         <v>3</v>
       </c>
@@ -1804,7 +1791,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15">
+    <row r="32" spans="1:9">
       <c r="A32" s="4">
         <v>3</v>
       </c>
@@ -1829,7 +1816,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" ht="15">
+    <row r="33" spans="1:9">
       <c r="A33" s="4">
         <v>4</v>
       </c>
@@ -1856,7 +1843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15">
+    <row r="34" spans="1:9">
       <c r="A34" s="4">
         <v>4</v>
       </c>
@@ -1885,7 +1872,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15">
+    <row r="35" spans="1:9">
       <c r="A35" s="4">
         <v>4</v>
       </c>
@@ -1914,7 +1901,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15">
+    <row r="36" spans="1:9">
       <c r="A36" s="4">
         <v>4</v>
       </c>
@@ -1943,7 +1930,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15">
+    <row r="37" spans="1:9">
       <c r="A37" s="4">
         <v>4</v>
       </c>
@@ -1972,7 +1959,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15">
+    <row r="38" spans="1:9">
       <c r="A38" s="4">
         <v>4</v>
       </c>
@@ -2001,7 +1988,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15">
+    <row r="39" spans="1:9">
       <c r="A39" s="4">
         <v>4</v>
       </c>
@@ -2030,7 +2017,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15">
+    <row r="40" spans="1:9">
       <c r="A40" s="4">
         <v>4</v>
       </c>
@@ -2059,7 +2046,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15">
+    <row r="41" spans="1:9">
       <c r="A41" s="4">
         <v>4</v>
       </c>
@@ -2088,7 +2075,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15">
+    <row r="42" spans="1:9">
       <c r="A42" s="4">
         <v>4</v>
       </c>
@@ -2113,7 +2100,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" ht="15">
+    <row r="43" spans="1:9">
       <c r="A43" s="4">
         <v>5</v>
       </c>
@@ -2140,7 +2127,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15">
+    <row r="44" spans="1:9">
       <c r="A44" s="4">
         <v>5</v>
       </c>
@@ -2169,7 +2156,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15">
+    <row r="45" spans="1:9">
       <c r="A45" s="4">
         <v>5</v>
       </c>
@@ -2198,7 +2185,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15">
+    <row r="46" spans="1:9">
       <c r="A46" s="4">
         <v>5</v>
       </c>
@@ -2227,7 +2214,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15">
+    <row r="47" spans="1:9">
       <c r="A47" s="4">
         <v>5</v>
       </c>
@@ -2256,7 +2243,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15">
+    <row r="48" spans="1:9">
       <c r="A48" s="4">
         <v>5</v>
       </c>
@@ -2285,7 +2272,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15">
+    <row r="49" spans="1:9">
       <c r="A49" s="4">
         <v>5</v>
       </c>
@@ -2314,7 +2301,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15">
+    <row r="50" spans="1:9">
       <c r="A50" s="4">
         <v>5</v>
       </c>
@@ -2343,7 +2330,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15">
+    <row r="51" spans="1:9">
       <c r="A51" s="4">
         <v>5</v>
       </c>
@@ -2368,7 +2355,7 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" ht="15">
+    <row r="52" spans="1:9">
       <c r="A52" s="4">
         <v>6</v>
       </c>
@@ -2395,7 +2382,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15">
+    <row r="53" spans="1:9">
       <c r="A53" s="4">
         <v>6</v>
       </c>
@@ -2424,7 +2411,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15">
+    <row r="54" spans="1:9">
       <c r="A54" s="4">
         <v>6</v>
       </c>
@@ -2453,7 +2440,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15">
+    <row r="55" spans="1:9">
       <c r="A55" s="4">
         <v>6</v>
       </c>
@@ -2482,7 +2469,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15">
+    <row r="56" spans="1:9">
       <c r="A56" s="4">
         <v>6</v>
       </c>
@@ -2511,7 +2498,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15">
+    <row r="57" spans="1:9">
       <c r="A57" s="4">
         <v>6</v>
       </c>
@@ -2540,7 +2527,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15">
+    <row r="58" spans="1:9">
       <c r="A58" s="4">
         <v>6</v>
       </c>
@@ -2569,7 +2556,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15">
+    <row r="59" spans="1:9">
       <c r="A59" s="4">
         <v>6</v>
       </c>
@@ -2598,7 +2585,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15">
+    <row r="60" spans="1:9">
       <c r="A60" s="4">
         <v>6</v>
       </c>
@@ -2627,7 +2614,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15">
+    <row r="61" spans="1:9">
       <c r="A61" s="4">
         <v>6</v>
       </c>
@@ -2652,7 +2639,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" ht="15">
+    <row r="62" spans="1:9">
       <c r="A62" s="4">
         <v>7</v>
       </c>
@@ -2677,7 +2664,7 @@
       </c>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9" ht="15">
+    <row r="63" spans="1:9">
       <c r="A63" s="4">
         <v>7</v>
       </c>
@@ -2702,7 +2689,7 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" ht="15">
+    <row r="64" spans="1:9">
       <c r="A64" s="4">
         <v>7</v>
       </c>
@@ -2729,7 +2716,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15">
+    <row r="65" spans="1:9">
       <c r="A65" s="4">
         <v>7</v>
       </c>
@@ -2754,7 +2741,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" ht="15">
+    <row r="66" spans="1:9">
       <c r="A66" s="4">
         <v>7</v>
       </c>
@@ -2779,7 +2766,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" ht="15">
+    <row r="67" spans="1:9">
       <c r="A67" s="4">
         <v>7</v>
       </c>
@@ -2804,7 +2791,7 @@
       </c>
       <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:9" ht="15">
+    <row r="68" spans="1:9">
       <c r="A68" s="4">
         <v>8</v>
       </c>
@@ -2829,7 +2816,7 @@
       </c>
       <c r="I68" s="3"/>
     </row>
-    <row r="69" spans="1:9" ht="15">
+    <row r="69" spans="1:9">
       <c r="A69" s="4">
         <v>8</v>
       </c>
@@ -2854,7 +2841,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" ht="15">
+    <row r="70" spans="1:9">
       <c r="A70" s="4">
         <v>8</v>
       </c>
@@ -2890,14 +2877,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
+    <row r="1" spans="1:5" ht="31.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2914,7 +2901,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15">
+    <row r="2" spans="1:5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2934,7 +2921,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15">
+    <row r="3" spans="1:5" ht="27.6">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -2943,18 +2930,18 @@
       </c>
       <c r="C3" s="7">
         <f>SUM(Planificación!H10:H20)</f>
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
+        <v>Revisar</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -2974,7 +2961,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -2994,7 +2981,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15">
+    <row r="6" spans="1:5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -3014,7 +3001,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -3034,7 +3021,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -3054,7 +3041,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15">
+    <row r="9" spans="1:5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -3081,22 +3068,22 @@
       <c r="D10" s="7"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="15">
+    <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
         <v>177</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="7">
         <f>SUM(C2:C9)</f>
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D11" s="7">
         <f>C11/60</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="E11" s="2" t="str">
         <f>IF(C11=720,"OK","Revisar")</f>
-        <v>OK</v>
+        <v>Revisar</v>
       </c>
     </row>
   </sheetData>
@@ -3118,14 +3105,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="76" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32" customHeight="1">
+    <row r="1" spans="1:3" ht="31.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -3136,7 +3123,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -3147,7 +3134,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30">
+    <row r="3" spans="1:3" ht="27.6">
       <c r="A3" s="2" t="s">
         <v>184</v>
       </c>
@@ -3158,7 +3145,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30">
+    <row r="4" spans="1:3" ht="27.6">
       <c r="A4" s="2" t="s">
         <v>187</v>
       </c>
@@ -3169,7 +3156,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30">
+    <row r="5" spans="1:3" ht="27.6">
       <c r="A5" s="2" t="s">
         <v>190</v>
       </c>
@@ -3180,7 +3167,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30">
+    <row r="6" spans="1:3" ht="27.6">
       <c r="A6" s="2" t="s">
         <v>193</v>
       </c>
@@ -3191,7 +3178,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30">
+    <row r="7" spans="1:3" ht="27.6">
       <c r="A7" s="2" t="s">
         <v>196</v>
       </c>
@@ -3202,7 +3189,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30">
+    <row r="8" spans="1:3" ht="27.6">
       <c r="A8" s="2" t="s">
         <v>199</v>
       </c>
